--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://recowin-my.sharepoint.com/personal/alexandra_savy_izi-by-edf_fr/Documents/Documents/PERSONNEL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{1611DFF5-0652-49BC-B1DE-CD9CA803C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0F7B92-5F7A-4B6C-98F8-11BE89B5E355}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{1611DFF5-0652-49BC-B1DE-CD9CA803C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90A53057-6B34-4486-8D94-2326777564A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95BAE555-5D9B-4C40-9273-CB03D3E2E169}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
   <si>
     <t>Nom de la recette</t>
   </si>
@@ -120,6 +120,195 @@
   </si>
   <si>
     <t>https://www.papillesetpupilles.fr/2009/03/salade-de-pommes-de-terre-aux-harengs.html/</t>
+  </si>
+  <si>
+    <t>Saint Jacques à la crème et au curry vert</t>
+  </si>
+  <si>
+    <t>Noix de St-Jacques, Ail, Curry, Crème</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2019/10/saint-jacques-la-creme-et-au-curry-vert.html?fbclid=IwAR0gRGIVnjIDsGkwQEU2cxW2d9B-P_2LI-bBmEwoj9RbPOkQNdpXyDkeXSY</t>
+  </si>
+  <si>
+    <t>Boulettes de thon</t>
+  </si>
+  <si>
+    <t>Thon, Œuf, Gruyère, Farine</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2020/04/boulettes-de-ton-rapides-recette-keto.html</t>
+  </si>
+  <si>
+    <t>Crevettes façon teriyaki</t>
+  </si>
+  <si>
+    <t>Crevettes, Riz, Avocat, Ail, Maïzena</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/02/28/crevettes-facon-teriyaki/</t>
+  </si>
+  <si>
+    <t>Filet de grondin poêlé à la provençale</t>
+  </si>
+  <si>
+    <t>Grondin, Tomates cerises, Courgette, Ail, Citron</t>
+  </si>
+  <si>
+    <t>https://www.petitsplatsentreamis.com/filets-de-grondin-poeles-a-la-provencale/</t>
+  </si>
+  <si>
+    <t>Bouillon miso aux nouilles et crevettes</t>
+  </si>
+  <si>
+    <t>Pousse de soja, Pois croquants, Crevettes, Nouilles de riz, Miso</t>
+  </si>
+  <si>
+    <t>https://www.elle.fr/Elle-a-Table/Recettes-de-cuisine/Soupe-miso-aux-legumes-aux-crevettes-et-aux-nouilles-737761</t>
+  </si>
+  <si>
+    <t>Filet de lieu noir et fondue de poireaux</t>
+  </si>
+  <si>
+    <t>Lieu noir, Poireaux, Crème, Echalote</t>
+  </si>
+  <si>
+    <t>https://adelepomme.wordpress.com/2018/03/18/dos-de-lieu-noir-et-fondue-de-poireaux/</t>
+  </si>
+  <si>
+    <t>Salade façon thaï aux pousses de soja tataki de saumon</t>
+  </si>
+  <si>
+    <t>Pousse de soja, Saumon, Crème, Citron vert</t>
+  </si>
+  <si>
+    <t>https://www.bridelice.fr/nos-recettes/salade-facon-thai-aux-pousses-de-soja-tartare-de-saumon</t>
+  </si>
+  <si>
+    <t>Noix de St-Jacques au chorizo sur lit de salade</t>
+  </si>
+  <si>
+    <t>Noix de St-Jacques, Chorizo</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2019/07/noix-de-st-jacques-au-chorizo-sur-lit.html?fbclid=IwAR0JBElEdQNtCPGWtGpJ12iWIoelVXFbW4WiW_0tvNNyL6QQAjv3hBzvz98</t>
+  </si>
+  <si>
+    <t>Sandwich au thon sans gluten</t>
+  </si>
+  <si>
+    <t>Thon, Œuf, Farine</t>
+  </si>
+  <si>
+    <t>https://www.sorcierefit.fr/recette/sandwich-sain-au-thon-sans-gluten</t>
+  </si>
+  <si>
+    <t>Pitas garnis à la truite grillée, aux tomates et aux herbes</t>
+  </si>
+  <si>
+    <t>Truite, Pitas, Houmous, Tomates, Citron vert, Oignon vert</t>
+  </si>
+  <si>
+    <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/poissons/pitas-garnis-a-la-truite-grillee-aux-tomates-aux-herbes/?fbclid=IwAR1Cni4SufPCzEdl6f7qNblh_isQ_f22X1sm1RrJxAHq24aQ6Ici7gcBZk8</t>
+  </si>
+  <si>
+    <t>Croque monsieur au thon</t>
+  </si>
+  <si>
+    <t>Pain, Thon, Cheddar</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_croque-monsieur-au-thon_15589.aspx</t>
+  </si>
+  <si>
+    <t>Linguine au saumon et petit pois</t>
+  </si>
+  <si>
+    <t>Pâtes, Saumon, Petit pois, Crème, Citron</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/linguine-au-saumon-et-petits-pois-192712?fbclid=IwAR0gFZr5bnsQl5G5EGXE2a9gPh91oNJjSQphfTP3OKKq5Rg9oLqhNft_lXE</t>
+  </si>
+  <si>
+    <t>Crevettes sautées ail gingembre et sauce soja</t>
+  </si>
+  <si>
+    <t>Crevettes, Ail</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2015/07/crevettes-sautees-lail-gingembre-et.html</t>
+  </si>
+  <si>
+    <t>Crevettes chorizo paprika</t>
+  </si>
+  <si>
+    <t>Crevettes, Poivron, Chorizo</t>
+  </si>
+  <si>
+    <t>http://www.kaderickenkuizinn.com/2014/04/recette-crevettes-chorizo-paprika/</t>
+  </si>
+  <si>
+    <t>Curry crevettes douceur au lait de coco</t>
+  </si>
+  <si>
+    <t>Crevettes, Lait de coco, Oignon, Curry</t>
+  </si>
+  <si>
+    <t>https://www.fourchette-et-bikini.fr/recettes/recettes-minceur/curry-de-crevette-douceur-au-lait-de-coco.html</t>
+  </si>
+  <si>
+    <t>Gambas flambées au rhum arrangé</t>
+  </si>
+  <si>
+    <t>Gambas, Rhum, Ail, Citron</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2019/06/gambas-flambees-au-rhum-arrange.html?fbclid=IwAR1bNnz7z9UdzbRezO5bEIe5gxJbTRD1IUOssmKVpMg_rgm0qlSSwL0riOk</t>
+  </si>
+  <si>
+    <t>Saumon vapeur au pesto vert</t>
+  </si>
+  <si>
+    <t>Saumon, Pesto</t>
+  </si>
+  <si>
+    <t>https://www.fourchette-et-bikini.fr/recettes/recettes-minceur/saumon-vapeur-au-pesto-vert.html</t>
+  </si>
+  <si>
+    <t>Riz au saumon</t>
+  </si>
+  <si>
+    <t>Saumon, Mirin, Riz, Oignon vert, Nori</t>
+  </si>
+  <si>
+    <t>https://cuisine-japonaise.com/recipe/salmon-no-tekone-zushi/</t>
+  </si>
+  <si>
+    <t>Pavé de saumon et pétoncles</t>
+  </si>
+  <si>
+    <t>Saumon, Coquille St-Jacques, Citron, Courgette</t>
+  </si>
+  <si>
+    <t>https://www.circulaire-en-ligne.ca/recette/pave-de-saumon-et-petoncles</t>
+  </si>
+  <si>
+    <t>Thon chermoula</t>
+  </si>
+  <si>
+    <t>Thon, Citron, Ail, Tomates cerises</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2018/10/thon-chermoula.html</t>
+  </si>
+  <si>
+    <t>Salades haricots blanc thon</t>
+  </si>
+  <si>
+    <t>Haricots blancs, Thon, Citron, Oignon rouge, Tomates cerises</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/07/salade-haricots-blancs-thon-recette-italienne.html</t>
   </si>
 </sst>
 </file>
@@ -198,7 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -208,6 +397,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -544,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3278A633-6FB3-4FFA-81F0-5904B4D7A089}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="44.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
@@ -557,7 +761,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -574,7 +778,7 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="5">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -591,7 +795,7 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="5">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -608,7 +812,7 @@
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -625,7 +829,7 @@
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="5">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -642,7 +846,7 @@
       <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="5">
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -659,7 +863,7 @@
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="5">
         <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -676,7 +880,7 @@
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="5">
         <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -686,15 +890,393 @@
         <v>26</v>
       </c>
     </row>
+    <row r="9" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7">
+        <v>15</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="5">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="5">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="5">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="5">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="5">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="5">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="5">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="5">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="5">
+        <v>20</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="5">
+        <v>20</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="5">
+        <v>20</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="5">
+        <v>20</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="5">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="5">
+        <v>20</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{6DD68AD2-868C-4E33-A20F-391529A8AC5A}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{6216C3A4-AC3A-47EB-AF6B-4FDEFCEFC638}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{D825979A-CA24-4B15-A496-34D2220FB3B6}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{F2C97E7B-46FB-4DB1-8693-09BBAA707B10}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{D2D76576-758C-4B57-BE95-CE73D683376D}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{F2CA23A5-7A9D-4255-B8F0-AFB77C3D0877}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{70F1810D-BEE8-4C90-8F64-C0DDEE0173AD}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{0A5BDF63-C85A-49CD-8707-CBFE99F0E8E4}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{ECD6228C-C305-4D0E-B0BF-757755B27058}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{2625FE79-BF1C-4DE1-97B8-F9E7BF10E9E8}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{DC42FEFD-1D73-4B0A-8852-17EBC149F2CB}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{DDDAEF1A-DC14-40B3-86FD-6A1ABA90AAA7}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{9D429885-B03D-45AF-8B49-EE0E58C8866F}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{4BFA8C61-A592-4CB3-B1DE-DF3825A86AEE}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{83B8A1BF-C741-48B3-9097-7C6FD642AD3E}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{676C8AA4-4A1B-4906-8F60-7E9E4039F6D8}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{99C0141B-E8E7-4661-9255-929BA22B9C26}"/>
+    <hyperlink ref="E12" r:id="rId11" xr:uid="{9A4AD5C1-F84B-4850-8915-FFEBB7B73365}"/>
+    <hyperlink ref="E13" r:id="rId12" xr:uid="{84AAFBB3-9BD0-4C68-8CFB-0C6609BB1186}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{BFF69DB9-9F22-4FBF-8297-87A946B60216}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{30F11626-EB86-40AB-96B0-A9BBF077F0D0}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{BF0B4334-E471-4283-8403-2555BB813885}"/>
+    <hyperlink ref="E17" r:id="rId16" xr:uid="{A46D77CC-82E3-451F-9A69-2B6ACD7A834F}"/>
+    <hyperlink ref="E18" r:id="rId17" xr:uid="{68A184AA-ED08-4C9D-8C4C-C1FE878FE0E8}"/>
+    <hyperlink ref="E19" r:id="rId18" xr:uid="{C8846D31-A8A2-4106-B1D9-29CD817DCBCE}"/>
+    <hyperlink ref="E20" r:id="rId19" xr:uid="{CAE8FC95-C7EB-49ED-8A1F-B64869F1216E}"/>
+    <hyperlink ref="E21" r:id="rId20" xr:uid="{C3BF87F9-EBDC-4763-AF4D-1D6A415D0758}"/>
+    <hyperlink ref="E23" r:id="rId21" xr:uid="{15F59080-4B28-41DF-AA40-AC2E877F8D12}"/>
+    <hyperlink ref="E24" r:id="rId22" xr:uid="{74CEEB04-6E40-4DAE-B769-3D30CC3712FA}"/>
+    <hyperlink ref="E25" r:id="rId23" xr:uid="{5725E0CB-63FF-4E82-997B-74E013B82F0B}"/>
+    <hyperlink ref="E26" r:id="rId24" xr:uid="{60DB50AB-ECCB-4A0F-B7EE-AC7217948BDD}"/>
+    <hyperlink ref="E27" r:id="rId25" xr:uid="{067D105D-8A09-477A-9677-B9F705D26822}"/>
+    <hyperlink ref="E28" r:id="rId26" xr:uid="{9303FA11-D4E9-4330-9443-839B714D955C}"/>
+    <hyperlink ref="E29" r:id="rId27" xr:uid="{354A71E9-04DF-49CE-A15B-ED13393D44BD}"/>
+    <hyperlink ref="E22" r:id="rId28" xr:uid="{EB40CBF2-F1EC-4970-AD46-77A45CFA5F0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://recowin-my.sharepoint.com/personal/alexandra_savy_izi-by-edf_fr/Documents/Documents/PERSONNEL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{1611DFF5-0652-49BC-B1DE-CD9CA803C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90A53057-6B34-4486-8D94-2326777564A6}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{1611DFF5-0652-49BC-B1DE-CD9CA803C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D0E6888-CCC2-48A2-B031-F3021C8AAAD6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95BAE555-5D9B-4C40-9273-CB03D3E2E169}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="323">
   <si>
     <t>Nom de la recette</t>
   </si>
@@ -89,36 +89,24 @@
     <t>Brochettes de crevettes citron vert curcuma</t>
   </si>
   <si>
-    <t>Crevettes, Citron vert, Ail</t>
-  </si>
-  <si>
     <t>https://www.fourchette-et-bikini.fr/recettes/recettes-minceur/brochettes-de-crevettes-au-citron-vert-et-au-curcuma.html</t>
   </si>
   <si>
     <t>Guedilles aux crevettes nordiques à l'avocat</t>
   </si>
   <si>
-    <t>Crevettes, Avocat, Ail, Citron, Pain, Salade</t>
-  </si>
-  <si>
     <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/fruits-de-mer/guedilles-aux-crevettes-nordiques-a-lavocat-a-la-fleur-dail/</t>
   </si>
   <si>
     <t>Couronne de crevettes aux épices à steak, sauce blanche</t>
   </si>
   <si>
-    <t>Crevettes, Oignon rouge, Citron, Fromage blanc, Ail</t>
-  </si>
-  <si>
     <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/fruits-de-mer/couronne-de-crevettes-aux-epices-a-steak-sauce-cocktail-blanche/?fbclid=IwAR148joTlnL6svriuI11dIB0ubbM9S7MrbXmmfhJyoFU1PviBenK_E6bnxU</t>
   </si>
   <si>
     <t>Salade de pommes de terre au hareng fumé</t>
   </si>
   <si>
-    <t>Pommes de terres, Hareng, Oignon rouge</t>
-  </si>
-  <si>
     <t>https://www.papillesetpupilles.fr/2009/03/salade-de-pommes-de-terre-aux-harengs.html/</t>
   </si>
   <si>
@@ -143,36 +131,24 @@
     <t>Crevettes façon teriyaki</t>
   </si>
   <si>
-    <t>Crevettes, Riz, Avocat, Ail, Maïzena</t>
-  </si>
-  <si>
     <t>https://clemfoodie.com/2019/02/28/crevettes-facon-teriyaki/</t>
   </si>
   <si>
     <t>Filet de grondin poêlé à la provençale</t>
   </si>
   <si>
-    <t>Grondin, Tomates cerises, Courgette, Ail, Citron</t>
-  </si>
-  <si>
     <t>https://www.petitsplatsentreamis.com/filets-de-grondin-poeles-a-la-provencale/</t>
   </si>
   <si>
     <t>Bouillon miso aux nouilles et crevettes</t>
   </si>
   <si>
-    <t>Pousse de soja, Pois croquants, Crevettes, Nouilles de riz, Miso</t>
-  </si>
-  <si>
     <t>https://www.elle.fr/Elle-a-Table/Recettes-de-cuisine/Soupe-miso-aux-legumes-aux-crevettes-et-aux-nouilles-737761</t>
   </si>
   <si>
     <t>Filet de lieu noir et fondue de poireaux</t>
   </si>
   <si>
-    <t>Lieu noir, Poireaux, Crème, Echalote</t>
-  </si>
-  <si>
     <t>https://adelepomme.wordpress.com/2018/03/18/dos-de-lieu-noir-et-fondue-de-poireaux/</t>
   </si>
   <si>
@@ -206,9 +182,6 @@
     <t>Pitas garnis à la truite grillée, aux tomates et aux herbes</t>
   </si>
   <si>
-    <t>Truite, Pitas, Houmous, Tomates, Citron vert, Oignon vert</t>
-  </si>
-  <si>
     <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/poissons/pitas-garnis-a-la-truite-grillee-aux-tomates-aux-herbes/?fbclid=IwAR1Cni4SufPCzEdl6f7qNblh_isQ_f22X1sm1RrJxAHq24aQ6Ici7gcBZk8</t>
   </si>
   <si>
@@ -233,27 +206,18 @@
     <t>Crevettes sautées ail gingembre et sauce soja</t>
   </si>
   <si>
-    <t>Crevettes, Ail</t>
-  </si>
-  <si>
     <t>https://www.leblogdecata.com/2015/07/crevettes-sautees-lail-gingembre-et.html</t>
   </si>
   <si>
     <t>Crevettes chorizo paprika</t>
   </si>
   <si>
-    <t>Crevettes, Poivron, Chorizo</t>
-  </si>
-  <si>
     <t>http://www.kaderickenkuizinn.com/2014/04/recette-crevettes-chorizo-paprika/</t>
   </si>
   <si>
     <t>Curry crevettes douceur au lait de coco</t>
   </si>
   <si>
-    <t>Crevettes, Lait de coco, Oignon, Curry</t>
-  </si>
-  <si>
     <t>https://www.fourchette-et-bikini.fr/recettes/recettes-minceur/curry-de-crevette-douceur-au-lait-de-coco.html</t>
   </si>
   <si>
@@ -296,19 +260,754 @@
     <t>Thon chermoula</t>
   </si>
   <si>
-    <t>Thon, Citron, Ail, Tomates cerises</t>
-  </si>
-  <si>
     <t>https://www.undejeunerdesoleil.com/2018/10/thon-chermoula.html</t>
   </si>
   <si>
     <t>Salades haricots blanc thon</t>
   </si>
   <si>
-    <t>Haricots blancs, Thon, Citron, Oignon rouge, Tomates cerises</t>
-  </si>
-  <si>
     <t>https://www.undejeunerdesoleil.com/2019/07/salade-haricots-blancs-thon-recette-italienne.html</t>
+  </si>
+  <si>
+    <t>Crevette, Citron vert, Ail</t>
+  </si>
+  <si>
+    <t>Crevette, Avocat, Ail, Citron, Pain, Salade</t>
+  </si>
+  <si>
+    <t>Crevette, Oignon rouge, Citron, Fromage blanc, Ail</t>
+  </si>
+  <si>
+    <t>Pomme de terre, Hareng, Oignon rouge</t>
+  </si>
+  <si>
+    <t>Crevette, Riz, Avocat, Ail, Maïzena</t>
+  </si>
+  <si>
+    <t>Grondin, Tomate cerise, Courgette, Ail, Citron</t>
+  </si>
+  <si>
+    <t>Pousse de soja, Pois croquant, Crevette, Nouilles de riz, Miso</t>
+  </si>
+  <si>
+    <t>Lieu noir, Poireau, Crème, Echalote</t>
+  </si>
+  <si>
+    <t>Truite, Pitas, Houmous, Tomate, Citron vert, Oignon vert</t>
+  </si>
+  <si>
+    <t>Crevette, Ail</t>
+  </si>
+  <si>
+    <t>Crevette, Poivron, Chorizo</t>
+  </si>
+  <si>
+    <t>Crevette, Lait de coco, Oignon, Curry</t>
+  </si>
+  <si>
+    <t>Thon, Citron, Ail, Tomate cerise</t>
+  </si>
+  <si>
+    <t>Haricot blanc, Thon, Citron, Oignon rouge, Tomate cerise</t>
+  </si>
+  <si>
+    <t>Tartare de saumon au sésame et crème d'avocat</t>
+  </si>
+  <si>
+    <t>Saumon, Echalote, Câpre, Cornichon, Citron vert</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/tartare-de-saumon-au-sesame-bergamote-et-creme-davocat-192180</t>
+  </si>
+  <si>
+    <t>Filet de saumon glacé au miel sur son lit de purée de brocolis</t>
+  </si>
+  <si>
+    <t>Saumon, Brocolis, Pomme de terre, Crème, Miel, Citron</t>
+  </si>
+  <si>
+    <t>https://www.fourchette-et-bikini.fr/recettes/recettes-minceur/filet-de-saumon-glace-au-miel-sur-son-lit-de-puree-de-brocolis.html</t>
+  </si>
+  <si>
+    <t>Filet de truite petits légumes</t>
+  </si>
+  <si>
+    <t>Truite, Carotte, Oignon rouge, Pois gourmand, Pomme de terre, Ail, Citron</t>
+  </si>
+  <si>
+    <t>https://www.petitsplatsentreamis.com/filet-de-truite-aux-petits-legumes/</t>
+  </si>
+  <si>
+    <t>Tagliatelles au saumon fumé et aux courgettes, sauce au boursin ail et fines herbes</t>
+  </si>
+  <si>
+    <t>Pâtes, Saumon, Courgette, Fromage frais</t>
+  </si>
+  <si>
+    <t>Courgettes farcies au thon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Courgette, Thon, Fromage frais, Echalote, Curry, Citron </t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/courgettes-farcies-au-thon-352272?fbclid=IwAR0vf62eCLQ_ji1wtB5YTD7FH0FC1wjlgx9MmDm2OWqYyWbS1t-EdyzJMvo</t>
+  </si>
+  <si>
+    <t>Poêlée de crevettes et d'épinards</t>
+  </si>
+  <si>
+    <t>Crevette, Epinard, Ail</t>
+  </si>
+  <si>
+    <t>https://jesuisuncuisinier.fr/fr/recette-de-poelee-depinards-sautes-aux-crevettes-un-plat-leger-et-delicieux/</t>
+  </si>
+  <si>
+    <t>Tagliatelles au saumon fumé, haricots verts et citron</t>
+  </si>
+  <si>
+    <t>Pâtes, Saumon, Haricot vert, Citron</t>
+  </si>
+  <si>
+    <t>Tacos aux crevettes épicées et mangue</t>
+  </si>
+  <si>
+    <t>Crevette, Orange, Tortillas, Chou rouge, Mangue, Tomate, Piment, Oignon rouge, Citron vert, Avocat, Crème</t>
+  </si>
+  <si>
+    <t>https://www.selection.ca/cuisine/recettes/recette-tacos-crevettes-epicees-salsa-mangue-avocat/</t>
+  </si>
+  <si>
+    <t>Omelette asiatique aux crevettes aux oignons verts</t>
+  </si>
+  <si>
+    <t>Œufs, Oignon vert, Crevette, Pousse de soja, Miel, Mayonnaise, Sriracha</t>
+  </si>
+  <si>
+    <t>https://www.troisfoisparjour.com/fr/recettes/dejeuners/oeufs/omelette-asiatique-aux-crevettes-aux-oignons-verts/</t>
+  </si>
+  <si>
+    <t>Salade d'avocat aux crevettes</t>
+  </si>
+  <si>
+    <t>Crevette, Salade, Oignon rouge, Avocat, Citron vert</t>
+  </si>
+  <si>
+    <t>https://feelgoodfoodie.net/recipe/shrimp-avocado-summer-salad/</t>
+  </si>
+  <si>
+    <t>Moules au chorizo</t>
+  </si>
+  <si>
+    <t>Moule, Chorizo, Echalote</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_moules-au-chorizo_47729.aspx#d61330-p1</t>
+  </si>
+  <si>
+    <t>Sardine poelée</t>
+  </si>
+  <si>
+    <t>Sardine, Farine, Riz</t>
+  </si>
+  <si>
+    <t>https://cuisine-japonaise.com/recipe/iwashi-no-kabayaki-don/</t>
+  </si>
+  <si>
+    <t>Saumon glacé au miso, riz, kale et avocat</t>
+  </si>
+  <si>
+    <t>Riz, Saumon, Citron vert, Miso, Miel, Chou kale, Riz, Avocat</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/01/28/saumon-glace-au-miso-riz-kale-et-avocat/</t>
+  </si>
+  <si>
+    <t>Soupe thai crevettes</t>
+  </si>
+  <si>
+    <t>Pâtes, Oignon, Ail, Citronelle, Carotte, Chou bok choy, Curry, Citron vert, Lait de coco, Crevette, Piment</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/11/07/soupe-thai-crevettes/</t>
+  </si>
+  <si>
+    <t>Concombre farcis au tartare de saumon</t>
+  </si>
+  <si>
+    <t>Concombre, Saumon, Crème, Citron, Câpre</t>
+  </si>
+  <si>
+    <t>https://www.troisfoisparjour.com/fr/recettes/entrees/tartares/concombres-farcis-au-tartare-de-saumon-au-boursin/</t>
+  </si>
+  <si>
+    <t>Filets de dorade marinées à l'estragon</t>
+  </si>
+  <si>
+    <t>Dorade, Citron vert, Citron jaune, Oignon vert, Tomate cerise</t>
+  </si>
+  <si>
+    <t>https://www.petitsplatsentreamis.com/filets-de-dorade-marinees-a-lestragon/</t>
+  </si>
+  <si>
+    <t>Moules marinières italienne</t>
+  </si>
+  <si>
+    <t>Moule, Ail, Vin blanc</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2018/08/moules-marinieres-italienne.html</t>
+  </si>
+  <si>
+    <t>Maquereaux au miso</t>
+  </si>
+  <si>
+    <t>Maquereau, Miso</t>
+  </si>
+  <si>
+    <t>https://www.justonecookbook.com/saba-misoni-simmered-mackerel-in-miso-sauce/</t>
+  </si>
+  <si>
+    <t>Filets de rougets au safran</t>
+  </si>
+  <si>
+    <t>Crème, Safran, Rouget, Fond de poisson, Echalote</t>
+  </si>
+  <si>
+    <t>https://m.marmiton.org/recettes/recette_filets-de-rouget-sauce-safranee_22231.aspx</t>
+  </si>
+  <si>
+    <t>Curry de cabillaud au lait de coco</t>
+  </si>
+  <si>
+    <t>Cabillaud, Echalote, Ananas, Curry, Lait de coco</t>
+  </si>
+  <si>
+    <t>https://www.elle.fr/Elle-a-Table/Recettes-de-cuisine/Curry-de-cabillaud-au-lait-de-coco-sucre-sale-3917946</t>
+  </si>
+  <si>
+    <t>Mille feuille d'aubergine et maquereau</t>
+  </si>
+  <si>
+    <t>Maquereau, Aubergine, Sauce tomate, Mozarella, Tomate cerise</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2019/05/mille-feuille-daubergine-et-maquereau.html?fbclid=IwAR1Ihwgv82OyR2Sa6pru1PBLPnZrfIOP1RCafbcm8CjLEThrS0lChDtMsF8</t>
+  </si>
+  <si>
+    <t>Blanquette de saumon légère &amp; carottes</t>
+  </si>
+  <si>
+    <t>Saumon, Carotte, Echalote, Citron, Crème</t>
+  </si>
+  <si>
+    <t>http://cococuistot.overblog.com/2017/08/blanquette-de-saumon-legere.html</t>
+  </si>
+  <si>
+    <t>Saumon glacé au sirop d'érable et épinard</t>
+  </si>
+  <si>
+    <t>Saumon, Sirop d'érable, Ail, Epinard</t>
+  </si>
+  <si>
+    <t>https://www.notparisienne.fr/plats/saumon-glace-au-sirop-derable/?fbclid=IwAR0i1wYBY2vcy_5_g8I5bL1DzJigEq-e9I4OkLFv9l9FmVhNa8dKnAEYDz8</t>
+  </si>
+  <si>
+    <t>Saumon à la toscane, épinards, artichauts et ail</t>
+  </si>
+  <si>
+    <t>Saumon, Ail, Tomate séchée, Artichaut, Câpre, Epinard, Crème</t>
+  </si>
+  <si>
+    <t>https://juliasalbum.com/creamy-tuscan-salmon/</t>
+  </si>
+  <si>
+    <t>Saumon glacé au miso, épinards et champignons</t>
+  </si>
+  <si>
+    <t>Miso, Miel, Saumon, Epinard, Champignon</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/15689/saumon-glace-au-miso--epinards-et-champignons?startAuto1=4</t>
+  </si>
+  <si>
+    <t>Bouillon thaï</t>
+  </si>
+  <si>
+    <t>Tomate, Crevette, Maïs, Citron vert, Echalote, Ail, Piment, Citronnelle</t>
+  </si>
+  <si>
+    <t>https://www.regal.fr/recettes/poissons-crustaces-et-fruits-de-mer/bouillon-thai-tom-yam-koung-16371?fbclid=IwAR38-s1tFjV7nwtG3gSoU6ZtrB-dyvZjwuWBdmIfoLZI4UE0TfAfPCCwOY0</t>
+  </si>
+  <si>
+    <t>Lotte sautées aux agrumes</t>
+  </si>
+  <si>
+    <t>Lotte, Orange, Citron, Citron vert, Clémentine</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/12/lotte-sautee-agrumes.html</t>
+  </si>
+  <si>
+    <t>Salade d'encornets aux agrumes et fenouil</t>
+  </si>
+  <si>
+    <t>Fenouil, Orange, Pamplemousse, Chorizo, Encornet, Oignon vert</t>
+  </si>
+  <si>
+    <t>https://cuisine-addict.com/salade-encornets-agrumes-fenouil/</t>
+  </si>
+  <si>
+    <t>Saumon aux bouillon thai et riz aux petits pois</t>
+  </si>
+  <si>
+    <t>Saumon, Riz, Petit pois, Champignon, Lait de coco, Citronnelle, Citron vert, Ail, Echalote, Curry</t>
+  </si>
+  <si>
+    <t>https://www.femmeactuelle.fr/cuisine/cuisine-des-chefs/tous-en-cuisine-la-recette-du-saumon-bouillon-thai-et-riz-aux-petits-pois-de-cyril-lignac-2093981?fbclid=IwAR1uQpqeHZrunEVAuFEKqmhxqKRyuwsasWwBZFimhboJryw9CMyjR1coePg#utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200428</t>
+  </si>
+  <si>
+    <t>Poisson et crevettes dans une sauce au lait de coco.</t>
+  </si>
+  <si>
+    <t>Cabillaud, Crevette, Ail, Oignon, Tomate, Poivron, Lait de coco, Citron vert, Piment</t>
+  </si>
+  <si>
+    <t>https://cuisine-addict.com/moqueca-peixe-e-camarao-specialite-bresilienne-poisson-crevettes/</t>
+  </si>
+  <si>
+    <t>Daurade mijotée à la sauce soja</t>
+  </si>
+  <si>
+    <t>Dorade, Poireau</t>
+  </si>
+  <si>
+    <t>https://cuisine-japonaise.com/recipe/tai-no-nitsuke-2/</t>
+  </si>
+  <si>
+    <t>Maquereau au miso</t>
+  </si>
+  <si>
+    <t>https://www.cuisine-japon.fr/recette-maquereau-au-miso-saba-no-miso-ni/</t>
+  </si>
+  <si>
+    <t>Truites en papillotes</t>
+  </si>
+  <si>
+    <t>Truite, Citron, Ail</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2019/05/truites-en-papillote-au-citron-thym-et.html?fbclid=IwAR0iUApkYafWHPbChwrDuyDYMgRD5jpbvf8Sk7Njh8MopOoR-gitu_Z3000</t>
+  </si>
+  <si>
+    <t>Courgette, Thon, Œuf, Ail, Chapelure, Parmesan, Poivron</t>
+  </si>
+  <si>
+    <t>https://www.platetrecette.fr/courgettes-farcie-thon/</t>
+  </si>
+  <si>
+    <t>Salade saumon sésame et au chia</t>
+  </si>
+  <si>
+    <t>Saumon, Graine de chia, Sésame, Œuf, Epinard, Melon, Oignon vert, Tomate cerise</t>
+  </si>
+  <si>
+    <t>http://www.lesrecettesdecaty.com/fr/recettes/plats-principaux/poisson-fruits-de-mer/salade-de-saumon-au-sesame-et-au-chia/</t>
+  </si>
+  <si>
+    <t>Filet de cabillaud au prosciutto tomates cerises</t>
+  </si>
+  <si>
+    <t>Cabillaud, Jambon sec, Tomate cerise, Ail</t>
+  </si>
+  <si>
+    <t>https://cuisine-addict.com/filet-cabillaud-prosciutto-tomates-cerise/</t>
+  </si>
+  <si>
+    <t>Crevettes sautées aux légumes</t>
+  </si>
+  <si>
+    <t>Crevette, Poivron, Carotte, Ail</t>
+  </si>
+  <si>
+    <t>https://cuisine.journaldesfemmes.fr/recette/312535-crevettes-sautees-aux-petits-legumes</t>
+  </si>
+  <si>
+    <t>Cannelloni poisson</t>
+  </si>
+  <si>
+    <t>Pâtes, Cabillaud, Crevette, Crème, Pain, Œuf, Ail, Citron, Lait</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/02/cannelloni-poisson.html</t>
+  </si>
+  <si>
+    <t>Risotto crevettes</t>
+  </si>
+  <si>
+    <t>Risotto, Crevette, Echalote, Vin blanc, Parmesan, Citron</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/03/risotto-crevettes-accord-mets-vins.html</t>
+  </si>
+  <si>
+    <t>Salade de pommes de terres aux harengs</t>
+  </si>
+  <si>
+    <t>Hareng, Pomme de terre, Pomme, Citron, Oignon rouge</t>
+  </si>
+  <si>
+    <t>https://www.petitsplatsentreamis.com/salade-de-pommes-de-terre-aux-harengs/</t>
+  </si>
+  <si>
+    <t>Saumon salé et grillé</t>
+  </si>
+  <si>
+    <t>Saumon</t>
+  </si>
+  <si>
+    <t>https://cuisine-japonaise.com/recipe/sake-no-shioyaki/</t>
+  </si>
+  <si>
+    <t>Chirashi saumon avocat</t>
+  </si>
+  <si>
+    <t>Riz rond, Saumon, Avocat, Oignon vert, Riz</t>
+  </si>
+  <si>
+    <t>https://www.petitsplatsentreamis.com/chirashi-de-saumon-et-avocat/</t>
+  </si>
+  <si>
+    <t>Saumon mariné au citron sur fondue de poireaux</t>
+  </si>
+  <si>
+    <t>Saumon, Poireau, Citron</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/saumon-marine-au-citron-sur-fondue-de-poireaux-187080</t>
+  </si>
+  <si>
+    <t>Boulette de poisson vapeur et sauce pimentée thaïe</t>
+  </si>
+  <si>
+    <t>Cabillaud, Citron vert, Œuf</t>
+  </si>
+  <si>
+    <t>https://www.fourchette-et-bikini.fr/recettes/recettes-minceur/boulettes-de-poisson-vapeur-allegees-et-sauce-pimentee-facon-thaie.html</t>
+  </si>
+  <si>
+    <t>Bar sauce meunière</t>
+  </si>
+  <si>
+    <t>Bar, Farine, Champignon, Navet, Sauce ponzu</t>
+  </si>
+  <si>
+    <t>https://cuisine-japonaise.com/recipe/suzuki-no-meuniere-butter-ponzu-sauce-zoe/</t>
+  </si>
+  <si>
+    <t>Courgettes farcies au saumon</t>
+  </si>
+  <si>
+    <t>Courgette, Saumon, Mozarella, Tomate, Vin blanc, Ail</t>
+  </si>
+  <si>
+    <t>https://www.jujube-en-cuisine.fr/courgettes-farcies-au-saumon/</t>
+  </si>
+  <si>
+    <t>Maquereaux à la fondue d'épinards</t>
+  </si>
+  <si>
+    <t>Maquereau, Radis, Vin blanc, Epinard, Crème</t>
+  </si>
+  <si>
+    <t>https://www.marieclaire.fr/cuisine/maquereaux-a-la-fondue-de-poireaux,1209871.asp?fbclid=IwAR2EsdZADKTIJzgrfCf69prFDqlANJKXdHbzACgDha_fgLZaXUcqyJBcj6Y</t>
+  </si>
+  <si>
+    <t>Filets de poisson blanc à l'orange, au fenouil et aux olives noires</t>
+  </si>
+  <si>
+    <t>Mayonnaise, Orange, Chapelure, Sole, Oignon rouge, Fenouil, Olive</t>
+  </si>
+  <si>
+    <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/poissons/filets-de-poisson-blanc-a-lorange-au-fenouil-aux-olives-noires/?fbclid=IwAR1Cni4SufPCzEdl6f7qNblh_isQ_f22X1sm1RrJxAHq24aQ6Ici7gcBZk8</t>
+  </si>
+  <si>
+    <t>Poisson au lait de coco</t>
+  </si>
+  <si>
+    <t>Tomate, Oignon, Dorade, Lait de coco</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_poisson-au-lait-de-coco_13238.aspx</t>
+  </si>
+  <si>
+    <t>Linguine seiches</t>
+  </si>
+  <si>
+    <t>Pâtes, Coulis de tomate, Oignon, Ail, Seiche, Piment</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/05/pates-linguine-seiches-italie.html</t>
+  </si>
+  <si>
+    <t>Filet de saumon aux amandes, caviar d'aubergines</t>
+  </si>
+  <si>
+    <t>Saumon, Amande effilée, Moutarde, Aubergine, Ail, Purée d'amande, Pomme, Citron, Radis, Poivron</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/10/filet-saumon-amandes-caviar-aubergines.html</t>
+  </si>
+  <si>
+    <t>Cabillaud, sauce au safran aux champignons et pommes de terres</t>
+  </si>
+  <si>
+    <t>Cabillaud, Pomme de terre, Champignons, Citron, Ail, Safran, Crème, Vin blanc</t>
+  </si>
+  <si>
+    <t>https://www.regal.fr/recettes/plats/cabillaud-sauce-safrane-aux-champignons-et-pommes-de-terre-17232</t>
+  </si>
+  <si>
+    <t>Saint Jacques à la crème de chou fleur</t>
+  </si>
+  <si>
+    <t>Chou-fleur, Pomme de terre, Oignon, Noix de St-Jacques, Curry, Crème, Noisette</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2018/12/saint-jacques-la-creme-de-chou-fleur.html?fbclid=IwAR14vBHPXdeFL2UZirMPSP7RHkKWTnBmeNczhvHgvOQ-u28D6VHCHLSmNYI</t>
+  </si>
+  <si>
+    <t>Velouté de chou fleur aux moules</t>
+  </si>
+  <si>
+    <t>Moules, Chou-fleur, Champignon, Pomme de terre, Oignon, Crème, Vin blanc</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/veloute-de-chou-fleur-et-moules-a-la-dieppoise-212783?utm_source=welcomingentreeplatdessert#</t>
+  </si>
+  <si>
+    <t>Gratin de courgettes aux anchois</t>
+  </si>
+  <si>
+    <t>Courgette, Ail, Anchois, Pesto, Œuf, Fromage frais, Lait, Tomate cerise, Poivron</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2020/04/gratin-des-courgettes-aux-anchois-et.html?fbclid=IwAR3krEchZq0saQTzprWRH9a2TnBP_4xgOnqWVJZoUwkqIn5W_HF7BHgqp4I</t>
+  </si>
+  <si>
+    <t>Saumon Pommes de terre hasselback</t>
+  </si>
+  <si>
+    <t>Pomme de terre, Saumon, Chou kale, Epinard, Citron</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/11/21/saumon-hasselback-kale/</t>
+  </si>
+  <si>
+    <t>Bisque de moules</t>
+  </si>
+  <si>
+    <t>Moule, Oignon, Ail, Carotte, Poireau, Crème, Tomate, Safran</t>
+  </si>
+  <si>
+    <t>https://www.mesinspirationsculinaires.com/article-bisque-de-moules-recette-facile.html?fbclid=IwAR12sSsOoGumrb4DD1HG2g5l8FyXu6rBJ24kk6GvNICapCJ7i8m_F5j9oXc</t>
+  </si>
+  <si>
+    <t>Bowl pommes de terre rôties saumon</t>
+  </si>
+  <si>
+    <t>Pomme de terre, Saumon fumé, Crème, Œuf de saumon, Epinard, Citron</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/12/12/bowl-pommes-de-terre-roties-saumon/</t>
+  </si>
+  <si>
+    <t>Risotto au saumon et à l'oseille</t>
+  </si>
+  <si>
+    <t>Saumon, Risotto, Parmesan, Oignon, Vin blanc</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/risotto-au-saumon-et-a-loseille-193308#utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200512</t>
+  </si>
+  <si>
+    <t>Parmentier thon et tomates</t>
+  </si>
+  <si>
+    <t>Pomme de terre, Thon, Oignon, Tomate, Coulis de tomate, Lait, Gruyère</t>
+  </si>
+  <si>
+    <t>http://www.amandinecooking.com/parmentier-au-thon-et-tomates.html?fbclid=IwAR2-yufDX65-ygOYgHLjDV4judmA1ya5Y8QEfnBTdXHWYfJV-cQyPqB0CM8</t>
+  </si>
+  <si>
+    <t>Hachis parmentier thon</t>
+  </si>
+  <si>
+    <t>Thon, Ail, Pomme de terre, Crème</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_hachis-parmentier-de-thon_72989.aspx</t>
+  </si>
+  <si>
+    <t>Soupe thaï de poisson</t>
+  </si>
+  <si>
+    <t>Echalote, Curry, Ail, Citronnelle, Fumée de poisson, Lait de coco, Crevette</t>
+  </si>
+  <si>
+    <t>https://www.femmeactuelle.fr/cuisine/recettes/entree/soupe-thai-de-poisson-03371?fbclid=IwAR1gIjpjFt74q0rpB651kly1d_gVTy_JT6SDecV6B67a3N-SmjI1KWxaPwE</t>
+  </si>
+  <si>
+    <t>Pâtes à l'espadon</t>
+  </si>
+  <si>
+    <t>Pâtes, Espadon, Tomate cerise, Aubergine, Raisin sec, Pignon de pin, Ail, Piment</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2018/08/pates-espadon-sicilienne.html</t>
+  </si>
+  <si>
+    <t>Salades de fruits de mer</t>
+  </si>
+  <si>
+    <t>Encornet, Palourde, Moule, Calamar, Céleri, Ail, Citron</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2019/06/salade-fruits-mer-insalata-di-mare.html</t>
+  </si>
+  <si>
+    <t>Soupe de saumon</t>
+  </si>
+  <si>
+    <t>Poireau, Carotte, Pomme de terre, Saumon, Crème</t>
+  </si>
+  <si>
+    <t>https://www.latendresseencuisine.com/soupe-de-saumon-lohikeitto-finlande/?fbclid=IwAR1bW-Yk8S1-qauXRcbhscv8KWceIZbOYewT2AhG25_ZZFLKRoUsV5OSepE</t>
+  </si>
+  <si>
+    <t>Cassolette de la mer</t>
+  </si>
+  <si>
+    <t>Moule, Dorade, Noix de St-Jacques, Vin blanc, Tomate, Oignon, Ciboulette, Champignon, Citron</t>
+  </si>
+  <si>
+    <t>https://karine-cuisine.blogspot.com/2014/12/la-cassolette-de-la-mer-et-sa-sauce.html</t>
+  </si>
+  <si>
+    <t>Tataki de saumon</t>
+  </si>
+  <si>
+    <t>Truite, Sésame</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2020/04/tataki-de-truite.html?fbclid=IwAR1wM2B_T2XVQOmuzIy9O7008qNmODps8dyigPoRMSACPk2IlZAsA7nrUX0</t>
+  </si>
+  <si>
+    <t>Blanquette de saumon</t>
+  </si>
+  <si>
+    <t>Saumon, Echalote, Carotte, Poireau, Champignon, Œuf, Citron, Moule, Fumet de poisson, Farine, Crème</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/blanquette-de-saumon-286121?utm_source=welcomingentreeplatdessert&amp;utm_medium=cpc&amp;utm_campaign=pmo_cac_article##</t>
+  </si>
+  <si>
+    <t>Soupe asiatique crevettes, légumes et nouilles</t>
+  </si>
+  <si>
+    <t>Poireau, Carotte, Navet, Citronnelle, Curry, Crevette, Nouille chinoise</t>
+  </si>
+  <si>
+    <t>http://cricrilespetitesdouceurs.com/article-soupe-asiatique-legere-complete-111954190.html</t>
+  </si>
+  <si>
+    <t>Salade de calamars au pamplemousse</t>
+  </si>
+  <si>
+    <t>Calamar, Asperge, Pousse de soja, Epinard, Pamplemousse</t>
+  </si>
+  <si>
+    <t>https://www.topsante.com/nutrition-et-recettes/recettes/salade-de-calamars-au-pamplemousse-comme-en-floride-59513</t>
+  </si>
+  <si>
+    <t>Papillote de truite</t>
+  </si>
+  <si>
+    <t>Truite, Fenouil, Chou romanesco, Citron</t>
+  </si>
+  <si>
+    <t>https://cuisine-addict.com/papillote-de-truite-au-fenouil-et-chou-romanesco/</t>
+  </si>
+  <si>
+    <t>Pot au feu léger au poisson</t>
+  </si>
+  <si>
+    <t>Saumon, Colin, Carotte, Poireau, Navet, Ail</t>
+  </si>
+  <si>
+    <t>https://cuisine-addict.com/pot-au-feu-leger-au-poisson/</t>
+  </si>
+  <si>
+    <t>Duo de harengs et blinis de pomme de terre</t>
+  </si>
+  <si>
+    <t>Hareng, Oignon rouge, Vinaigre de cidre, Yaourt grec, Citron</t>
+  </si>
+  <si>
+    <t>https://plaisiretequilibre.wordpress.com/2018/04/10/duo-de-harengs-et-ses-blinis-de-pomme-de-terre/</t>
+  </si>
+  <si>
+    <t>Salade Encornets agrume fenouil</t>
+  </si>
+  <si>
+    <t>Encornet, Tomate cerise, Poivron, Ail, Citron</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/petite-salade-d-encornets-au-cumin-198006</t>
+  </si>
+  <si>
+    <t>Papillotes de maquereaux</t>
+  </si>
+  <si>
+    <t>Tomate, Maquereau, Citron</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_papillotes-de-maquereau_14593.aspx</t>
+  </si>
+  <si>
+    <t>Sardine à la macoraine</t>
+  </si>
+  <si>
+    <t>Piment, Farine, Sardine, Citron, Ail</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_sardines-a-la-marocaine_325909.aspx</t>
+  </si>
+  <si>
+    <t>Pâtes à la vénitienne</t>
+  </si>
+  <si>
+    <t>Pâtes, Oignon, Anchois, Vin blanc</t>
+  </si>
+  <si>
+    <t>https://www.undejeunerdesoleil.com/2018/02/pates-venitienne-bigoli-salsa.html</t>
+  </si>
+  <si>
+    <t>Boulettes de thon simple</t>
+  </si>
+  <si>
+    <t>Thon, Ail, Chapelure, Œuf</t>
+  </si>
+  <si>
+    <t>https://www.marmiton.org/recettes/recette_boulettes-de-thon-simple_309595.aspx</t>
+  </si>
+  <si>
+    <t>Salade de poulpes</t>
+  </si>
+  <si>
+    <t>Encornet, Citron, Ail</t>
+  </si>
+  <si>
+    <t>https://www.recettesduchef.fr/Recettes/Salades/salade-de-poulpe.html</t>
   </si>
 </sst>
 </file>
@@ -748,7 +1447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3278A633-6FB3-4FFA-81F0-5904B4D7A089}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="44.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
@@ -827,7 +1526,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C5" s="5">
         <v>11</v>
@@ -836,15 +1535,15 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C6" s="5">
         <v>12</v>
@@ -853,15 +1552,15 @@
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C7" s="5">
         <v>15</v>
@@ -870,15 +1569,15 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="C8" s="5">
         <v>15</v>
@@ -887,15 +1586,15 @@
         <v>7</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5">
         <v>15</v>
@@ -904,15 +1603,15 @@
         <v>7</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5">
         <v>15</v>
@@ -921,15 +1620,15 @@
         <v>7</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="C11" s="5">
         <v>15</v>
@@ -938,15 +1637,15 @@
         <v>7</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C12" s="5">
         <v>15</v>
@@ -955,15 +1654,15 @@
         <v>7</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C13" s="7">
         <v>15</v>
@@ -972,15 +1671,15 @@
         <v>7</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="C14" s="5">
         <v>15</v>
@@ -989,15 +1688,15 @@
         <v>7</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C15" s="5">
         <v>15</v>
@@ -1006,15 +1705,15 @@
         <v>7</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C16" s="5">
         <v>15</v>
@@ -1023,15 +1722,15 @@
         <v>7</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C17" s="5">
         <v>15</v>
@@ -1040,15 +1739,15 @@
         <v>7</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C18" s="5">
         <v>15</v>
@@ -1057,15 +1756,15 @@
         <v>7</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C19" s="5">
         <v>18</v>
@@ -1074,15 +1773,15 @@
         <v>7</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5">
         <v>18</v>
@@ -1091,15 +1790,15 @@
         <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C21" s="5">
         <v>20</v>
@@ -1108,15 +1807,15 @@
         <v>7</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C22" s="5">
         <v>20</v>
@@ -1125,15 +1824,15 @@
         <v>7</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C23" s="5">
         <v>20</v>
@@ -1142,15 +1841,15 @@
         <v>7</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C24" s="5">
         <v>20</v>
@@ -1159,15 +1858,15 @@
         <v>7</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C25" s="5">
         <v>20</v>
@@ -1176,15 +1875,15 @@
         <v>7</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C26" s="5">
         <v>20</v>
@@ -1193,15 +1892,15 @@
         <v>7</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C27" s="5">
         <v>20</v>
@@ -1210,15 +1909,15 @@
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C28" s="5">
         <v>20</v>
@@ -1227,15 +1926,15 @@
         <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C29" s="5">
         <v>20</v>
@@ -1244,7 +1943,1346 @@
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="5">
+        <v>20</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="5">
+        <v>20</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="5">
+        <v>20</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="5">
+        <v>20</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="5">
+        <v>20</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="5">
+        <v>20</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="5">
+        <v>20</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="5">
+        <v>20</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="5">
+        <v>20</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="5">
+        <v>20</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="5">
+        <v>25</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="5">
+        <v>25</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="5">
+        <v>25</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="5">
+        <v>25</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="5">
+        <v>25</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="5">
+        <v>30</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="5">
+        <v>30</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="5">
+        <v>30</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="5">
+        <v>30</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="5">
+        <v>30</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="5">
+        <v>30</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="5">
+        <v>30</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="5">
+        <v>30</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="5">
+        <v>30</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="5">
+        <v>30</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="5">
+        <v>30</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" s="5">
+        <v>30</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" s="5">
+        <v>30</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="5">
+        <v>30</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="5">
+        <v>30</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" s="5">
+        <v>35</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="5">
+        <v>35</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="5">
+        <v>35</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="5">
+        <v>35</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" s="5">
+        <v>35</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" s="5">
+        <v>35</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" s="5">
+        <v>38</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" s="5">
+        <v>40</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C68" s="5">
+        <v>40</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="5">
+        <v>40</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" s="5">
+        <v>40</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" s="5">
+        <v>40</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" s="5">
+        <v>40</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" s="5">
+        <v>42</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" s="5">
+        <v>45</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" s="5">
+        <v>45</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" s="5">
+        <v>45</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C77" s="5">
+        <v>45</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78" s="5">
+        <v>50</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" s="5">
+        <v>50</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" s="5">
+        <v>50</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C81" s="5">
+        <v>50</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C82" s="5">
+        <v>50</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C83" s="5">
+        <v>50</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C84" s="5">
+        <v>50</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" s="5">
+        <v>55</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" s="5">
+        <v>55</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C87" s="5">
+        <v>55</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88" s="5">
+        <v>55</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C89" s="5">
+        <v>55</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" s="5">
+        <v>60</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C91" s="5">
+        <v>60</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C92" s="5">
+        <v>60</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C93" s="5">
+        <v>60</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C94" s="5">
+        <v>70</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C95" s="5">
+        <v>75</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C96" s="5">
+        <v>10</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C97" s="5">
+        <v>30</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C98" s="5">
+        <v>40</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C99" s="5">
+        <v>20</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C100" s="5">
+        <v>35</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C101" s="5">
+        <v>45</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C102" s="5">
+        <v>30</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C103" s="5">
+        <v>35</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C104" s="5">
+        <v>45</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C105" s="5">
+        <v>25</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C106" s="5">
+        <v>45</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C107" s="5">
+        <v>50</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C108" s="5">
+        <v>25</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://recowin-my.sharepoint.com/personal/alexandra_savy_izi-by-edf_fr/Documents/Documents/PERSONNEL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{1611DFF5-0652-49BC-B1DE-CD9CA803C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D0E6888-CCC2-48A2-B031-F3021C8AAAD6}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{1611DFF5-0652-49BC-B1DE-CD9CA803C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{870FA428-3C29-4FCE-AA56-F83308430A95}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95BAE555-5D9B-4C40-9273-CB03D3E2E169}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="406">
   <si>
     <t>Nom de la recette</t>
   </si>
@@ -761,9 +761,6 @@
     <t>Cabillaud, sauce au safran aux champignons et pommes de terres</t>
   </si>
   <si>
-    <t>Cabillaud, Pomme de terre, Champignons, Citron, Ail, Safran, Crème, Vin blanc</t>
-  </si>
-  <si>
     <t>https://www.regal.fr/recettes/plats/cabillaud-sauce-safrane-aux-champignons-et-pommes-de-terre-17232</t>
   </si>
   <si>
@@ -1008,6 +1005,258 @@
   </si>
   <si>
     <t>https://www.recettesduchef.fr/Recettes/Salades/salade-de-poulpe.html</t>
+  </si>
+  <si>
+    <t>Cabillaud, Pomme de terre, Champignon, Citron, Ail, Safran, Crème, Vin blanc</t>
+  </si>
+  <si>
+    <t>Nouilles thaïlandaises épicées</t>
+  </si>
+  <si>
+    <t>Pâtes, Œuf, Courgette, Champignon, Ail, Sriracha, Oignon vert, Cacahuète</t>
+  </si>
+  <si>
+    <t>Végétarien</t>
+  </si>
+  <si>
+    <t>https://chefcuisto.com/recette/nouilles-thailandaises-epicees-style-one-pot/?fbclid=IwAR0YbzNqlE4UTPzTpjevoWQBMMcLTfSDyJXvc6pGDMwJnOrwRg0Ahgct7N8</t>
+  </si>
+  <si>
+    <t>One pot pasta au soja, kale et coco</t>
+  </si>
+  <si>
+    <t>Chou kale, Oignon vert, Ail, Protéine de soja, Pâtes, Lait de coco, Avocat</t>
+  </si>
+  <si>
+    <t>Vegan</t>
+  </si>
+  <si>
+    <t>https://www.healthyjulia.com/2019/02/one-pan-pasta-au-soja-kale-et-coco-vegan.html?m=1&amp;fbclid=IwAR0mqizm3nzWKmGwTNKjyX_f23zm8_vPPkCGIqeriBXwpWSqA-w507pHIe8</t>
+  </si>
+  <si>
+    <t>Parmentier cèpes/champignons</t>
+  </si>
+  <si>
+    <t>Pomme de terre, Patate douce, Céleri, Oignon, Ail, Champignon, Lait, Crème, Maïzena</t>
+  </si>
+  <si>
+    <t>https://www.tastinggoodnaturally.com/parmentier-vegetalien-aux-cepes-et-champignons-de-paris/</t>
+  </si>
+  <si>
+    <t>Pita purée de butternut, haricot rouges et avocats</t>
+  </si>
+  <si>
+    <t>Pain pita, Avocat, Ail, Crème, Citron, Oignon vert, Haricot rouge</t>
+  </si>
+  <si>
+    <t>https://menu-vegetarien.com/recettes/pains-pita-avocat-haricots-rouges/</t>
+  </si>
+  <si>
+    <t>Soupe au miso au chou chinois et oeuf poché</t>
+  </si>
+  <si>
+    <t>Pâtes, Œuf, Chou pak-choï, Oignon vert, Echalote, Miso</t>
+  </si>
+  <si>
+    <t>https://www.japancentre.com/fr/recipes/1526-miso-ramen-soup-with-pakchoi-and-poached-egg?fbclid=IwAR0Pe8DMYfxV-TV8l2HjGL56lrXjNn03GGdFmSdjjLBmRxM-BP-pshKXjCs</t>
+  </si>
+  <si>
+    <t>Tartines avocat, fromage et fines herbes</t>
+  </si>
+  <si>
+    <t>Pain, Œuf, Avocat, Fromage frais</t>
+  </si>
+  <si>
+    <t>https://cuisine-addict.com/tartines-avocat-fromage-oeuf-mollet/</t>
+  </si>
+  <si>
+    <t>Wrap végétarien à la mexicaine</t>
+  </si>
+  <si>
+    <t>Wrap, Haricot rouge, Emincé de soja, Avocat, Fromage, Coulis de tomate</t>
+  </si>
+  <si>
+    <t>https://vegan-pratique.fr/recettes/wrap-vegetarien-a-la-mexicaine/?fbclid=IwAR1gIjpjFt74q0rpB651kly1d_gVTy_JT6SDecV6B67a3N-SmjI1KWxaPwE</t>
+  </si>
+  <si>
+    <t>Spaghetti de courgettes au pesto d'avocats</t>
+  </si>
+  <si>
+    <t>Avocat, Basilic, Ail, Citron, Pignon, Courgette, Tomate cerise</t>
+  </si>
+  <si>
+    <t>http://cookalifebymaeva.blogspot.com/2016/07/zoodles-spaghetti-de-courgettes-au-pesto-d-avocat-et-tomates-cerises.html</t>
+  </si>
+  <si>
+    <t>Tofu croustillant à la sauce aigre douce</t>
+  </si>
+  <si>
+    <t>Maïzena, Ketchup, Orange, Sriracha, Tofu</t>
+  </si>
+  <si>
+    <t>https://www.mangoandsalt.com/2015/12/02/tofu-croustillant-a-la-sauce-aigre-douce/</t>
+  </si>
+  <si>
+    <t>Salade de pâtes au pesto</t>
+  </si>
+  <si>
+    <t>Pâtes, Pesto, Tomate cerise, Petit pois, Mozzarella</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/04/29/salade-de-pates-au-pesto/</t>
+  </si>
+  <si>
+    <t>Spaghetti à l'ail, tomates caramélisées et burrata</t>
+  </si>
+  <si>
+    <t>Pâtes, Tomate cerise, Ail, Mozzarella, Basilic</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/08/20/spaghetti-a-lail-tomates-caramelisees-et-burrata/</t>
+  </si>
+  <si>
+    <t>Omelette roulée japonaise</t>
+  </si>
+  <si>
+    <t>Œuf, Dashi</t>
+  </si>
+  <si>
+    <t>https://www.itadakimasu.fr/recettes/recette-express-tamagoyaki-lomelette-roulee-japonaise</t>
+  </si>
+  <si>
+    <t>Omelette colombienne</t>
+  </si>
+  <si>
+    <t>Œuf, Tomate, Oignon vert, Emmental</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2019/07/omelette-la-colombienne-huevos-pericos.html</t>
+  </si>
+  <si>
+    <t>Omelette aux girolles</t>
+  </si>
+  <si>
+    <t>Œuf, Champignon</t>
+  </si>
+  <si>
+    <t>https://www.leblogdecata.com/2020/09/omelette-aux-girolles.html</t>
+  </si>
+  <si>
+    <t>Croque monsieur aux asperges</t>
+  </si>
+  <si>
+    <t>Pain, Asperge, Pesto, Roquette, Cantal</t>
+  </si>
+  <si>
+    <t>https://www.lespepitesdenoisette.fr/les-recettes/croque-monsieur-aux-asperges/</t>
+  </si>
+  <si>
+    <t>Wrap au houmous</t>
+  </si>
+  <si>
+    <t>Wrap, Houmous, Avocat, Carotte, Cranberrie, Graine, Oignon vert, Salade, Citron</t>
+  </si>
+  <si>
+    <t>https://www.lespepitesdenoisette.fr/les-recettes/veggie-wrap-au-houmous/</t>
+  </si>
+  <si>
+    <t>Tagliatelle à l'ail, citron et huile d'olive</t>
+  </si>
+  <si>
+    <t>Pâtes, Ail, Citron</t>
+  </si>
+  <si>
+    <t>https://www.mangoandsalt.com/2019/06/14/tagliatelle-a-lail-citron-huile-dolive/</t>
+  </si>
+  <si>
+    <t>Bol de vermicelles, ananas, concombre, menthe, noix de cajou et avocat</t>
+  </si>
+  <si>
+    <t>Nouille de riz, Ananas, Concombre, Menthe, Avocat, Citron vert, Echalote</t>
+  </si>
+  <si>
+    <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/salades-et-bols/bol-de-vermicelles-ananas-concombre-menthe-noix-de-cajou-avocat/?fbclid=IwAR3qqdKZDkdR4z3dZE6Rgx-_6c7GU27Q-VPx-VHbeERFyoJ2aw2liEmtN4g</t>
+  </si>
+  <si>
+    <t>Bo bun vegan</t>
+  </si>
+  <si>
+    <t>Nouille de riz, Protéine de soja texturé, Carotte, Concombre, Cacahuète, Miso, Beurre de cacahuète, Citron, Purée de piment, Menthe</t>
+  </si>
+  <si>
+    <t>https://www.100-vegetal.com/2013/04/bo-bun-vegan.html</t>
+  </si>
+  <si>
+    <t>Chou à la tomate et aux épices cajuns</t>
+  </si>
+  <si>
+    <t>Chou, Oignon, Ail, Tomate concassée</t>
+  </si>
+  <si>
+    <t>http://www.amandinecooking.com/chou-tomate-cajun.html?utm_source=_ob_email&amp;utm_medium=_ob_notification&amp;utm_campaign=_ob_pushmail</t>
+  </si>
+  <si>
+    <t>Aloo Shimla - Pommes de terres et poivron</t>
+  </si>
+  <si>
+    <t>Poivron, Pomme de terre</t>
+  </si>
+  <si>
+    <t>http://www.pankaj-blog.com/article-recette-indienne-aloo-shimla-mirch-video-118567829.html</t>
+  </si>
+  <si>
+    <t>Spaghetti carbonara végétarienne</t>
+  </si>
+  <si>
+    <t>Pâtes, Champignon, Ail, Parmesan, Œuf, Lait</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/10/02/spaghetti-carbonara-vegetarienne/</t>
+  </si>
+  <si>
+    <t>Grilled cheese à la pomme et comté</t>
+  </si>
+  <si>
+    <t>Oignon, Pomme, Pain, Comté</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/11/27/grilled-cheese/</t>
+  </si>
+  <si>
+    <t>Soupe nouilles soba blettes champignon</t>
+  </si>
+  <si>
+    <t>Champignon, Ail, Sriracha, Nouille Soba, Blette</t>
+  </si>
+  <si>
+    <t>https://menu-vegetarien.com/recettes/soupe-nouilles-soba-blettes-champignons/</t>
+  </si>
+  <si>
+    <t>Ravioles de royan à la coriandre et au piment</t>
+  </si>
+  <si>
+    <t>Raviole de Royan, Carotte, Crème, Parmesan, Piment</t>
+  </si>
+  <si>
+    <t>https://www.cuisineactuelle.fr/recettes/ravioles-de-royans-a-la-coriandre-et-au-piment-192747?fbclid=IwAR2Y0EPQx-oUAScCrcQDz4dXwHvIJopf0u0_nYjGCt9yN1KGGOkLMzfraT4#utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200326</t>
+  </si>
+  <si>
+    <t>Sauté asiatique à la protéine végétale texturée</t>
+  </si>
+  <si>
+    <t>Protéine de soja texturée, Pâtes, Brocoli, Ail, Petit pois</t>
+  </si>
+  <si>
+    <t>https://www.troisfoisparjour.com/fr/recettes/plats-principaux/tofu-et-soya/saute-asiatique-a-la-proteine-vegetale-texturee-pvt/?fbclid=IwAR0cdND3Hz_cgEtuInUqJD-VLLdZkf3P90UM6hUmtSOmG7HiIG3AsK5W4eU</t>
+  </si>
+  <si>
+    <t>Soupe inspiration asiatique</t>
+  </si>
+  <si>
+    <t>Nouille Soba, Œuf, Chou bok-choï, Miso, Citronnelle, Citron vert</t>
+  </si>
+  <si>
+    <t>https://clemfoodie.com/2019/02/22/soupe-dinspiration-asiatique/</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1111,6 +1360,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1447,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3278A633-6FB3-4FFA-81F0-5904B4D7A089}">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="44.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
@@ -1657,7 +1909,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" s="9" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>33</v>
       </c>
@@ -2001,7 +2253,7 @@
       <c r="A33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="6" t="s">
         <v>100</v>
       </c>
       <c r="C33" s="5">
@@ -2418,20 +2670,20 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:5" s="9" customFormat="1" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="7">
         <v>30</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="D58" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2814,7 +3066,7 @@
         <v>239</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>240</v>
+        <v>322</v>
       </c>
       <c r="C81" s="5">
         <v>50</v>
@@ -2823,15 +3075,15 @@
         <v>7</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="C82" s="5">
         <v>50</v>
@@ -2840,15 +3092,15 @@
         <v>7</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="C83" s="5">
         <v>50</v>
@@ -2857,15 +3109,15 @@
         <v>7</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="C84" s="5">
         <v>50</v>
@@ -2874,15 +3126,15 @@
         <v>7</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="C85" s="5">
         <v>55</v>
@@ -2891,15 +3143,15 @@
         <v>7</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="C86" s="5">
         <v>55</v>
@@ -2908,15 +3160,15 @@
         <v>7</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="C87" s="5">
         <v>55</v>
@@ -2925,15 +3177,15 @@
         <v>7</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="C88" s="5">
         <v>55</v>
@@ -2942,15 +3194,15 @@
         <v>7</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="C89" s="5">
         <v>55</v>
@@ -2959,15 +3211,15 @@
         <v>7</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="C90" s="5">
         <v>60</v>
@@ -2976,15 +3228,15 @@
         <v>7</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="C91" s="5">
         <v>60</v>
@@ -2993,15 +3245,15 @@
         <v>7</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="C92" s="5">
         <v>60</v>
@@ -3010,15 +3262,15 @@
         <v>7</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="C93" s="5">
         <v>60</v>
@@ -3027,15 +3279,15 @@
         <v>7</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="C94" s="5">
         <v>70</v>
@@ -3044,15 +3296,15 @@
         <v>7</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C95" s="5">
         <v>75</v>
@@ -3061,15 +3313,15 @@
         <v>7</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="C96" s="5">
         <v>10</v>
@@ -3078,15 +3330,15 @@
         <v>7</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="C97" s="5">
         <v>30</v>
@@ -3095,15 +3347,15 @@
         <v>7</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="C98" s="5">
         <v>40</v>
@@ -3112,15 +3364,15 @@
         <v>7</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="C99" s="5">
         <v>20</v>
@@ -3129,15 +3381,15 @@
         <v>7</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="C100" s="5">
         <v>35</v>
@@ -3146,15 +3398,15 @@
         <v>7</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="C101" s="5">
         <v>45</v>
@@ -3163,15 +3415,15 @@
         <v>7</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="C102" s="5">
         <v>30</v>
@@ -3180,15 +3432,15 @@
         <v>7</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="C103" s="5">
         <v>35</v>
@@ -3197,15 +3449,15 @@
         <v>7</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="C104" s="5">
         <v>45</v>
@@ -3214,15 +3466,15 @@
         <v>7</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="C105" s="5">
         <v>25</v>
@@ -3231,15 +3483,15 @@
         <v>7</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="C106" s="5">
         <v>45</v>
@@ -3248,15 +3500,15 @@
         <v>7</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="C107" s="5">
         <v>50</v>
@@ -3265,15 +3517,15 @@
         <v>7</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="C108" s="5">
         <v>25</v>
@@ -3282,39 +3534,602 @@
         <v>7</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C109" s="5">
+        <v>15</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C110" s="5">
+        <v>15</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C111" s="5">
+        <v>15</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C112" s="5">
+        <v>15</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C113" s="5">
+        <v>15</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C114" s="5">
+        <v>15</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C115" s="5">
+        <v>15</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C116" s="5">
+        <v>15</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C117" s="5">
+        <v>15</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C118" s="5">
+        <v>15</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C119" s="5">
+        <v>15</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C120" s="5">
+        <v>15</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C121" s="5">
+        <v>15</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C122" s="5">
+        <v>15</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C123" s="5">
+        <v>15</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C124" s="5">
+        <v>15</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C125" s="5">
+        <v>15</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C126" s="5">
+        <v>18</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C127" s="5">
+        <v>20</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" s="9" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C128" s="7">
+        <v>20</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C129" s="5">
+        <v>20</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C130" s="5">
+        <v>20</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C131" s="5">
+        <v>20</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C132" s="5">
+        <v>20</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C133" s="5">
+        <v>25</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C134" s="5">
+        <v>25</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C135" s="5">
+        <v>25</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{0A5BDF63-C85A-49CD-8707-CBFE99F0E8E4}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{ECD6228C-C305-4D0E-B0BF-757755B27058}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{2625FE79-BF1C-4DE1-97B8-F9E7BF10E9E8}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{DC42FEFD-1D73-4B0A-8852-17EBC149F2CB}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{DDDAEF1A-DC14-40B3-86FD-6A1ABA90AAA7}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{9D429885-B03D-45AF-8B49-EE0E58C8866F}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{4BFA8C61-A592-4CB3-B1DE-DF3825A86AEE}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{83B8A1BF-C741-48B3-9097-7C6FD642AD3E}"/>
-    <hyperlink ref="E10" r:id="rId9" xr:uid="{676C8AA4-4A1B-4906-8F60-7E9E4039F6D8}"/>
-    <hyperlink ref="E11" r:id="rId10" xr:uid="{99C0141B-E8E7-4661-9255-929BA22B9C26}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{9A4AD5C1-F84B-4850-8915-FFEBB7B73365}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{84AAFBB3-9BD0-4C68-8CFB-0C6609BB1186}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{BFF69DB9-9F22-4FBF-8297-87A946B60216}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{30F11626-EB86-40AB-96B0-A9BBF077F0D0}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{BF0B4334-E471-4283-8403-2555BB813885}"/>
-    <hyperlink ref="E17" r:id="rId16" xr:uid="{A46D77CC-82E3-451F-9A69-2B6ACD7A834F}"/>
-    <hyperlink ref="E18" r:id="rId17" xr:uid="{68A184AA-ED08-4C9D-8C4C-C1FE878FE0E8}"/>
-    <hyperlink ref="E19" r:id="rId18" xr:uid="{C8846D31-A8A2-4106-B1D9-29CD817DCBCE}"/>
-    <hyperlink ref="E20" r:id="rId19" xr:uid="{CAE8FC95-C7EB-49ED-8A1F-B64869F1216E}"/>
-    <hyperlink ref="E21" r:id="rId20" xr:uid="{C3BF87F9-EBDC-4763-AF4D-1D6A415D0758}"/>
-    <hyperlink ref="E23" r:id="rId21" xr:uid="{15F59080-4B28-41DF-AA40-AC2E877F8D12}"/>
-    <hyperlink ref="E24" r:id="rId22" xr:uid="{74CEEB04-6E40-4DAE-B769-3D30CC3712FA}"/>
-    <hyperlink ref="E25" r:id="rId23" xr:uid="{5725E0CB-63FF-4E82-997B-74E013B82F0B}"/>
-    <hyperlink ref="E26" r:id="rId24" xr:uid="{60DB50AB-ECCB-4A0F-B7EE-AC7217948BDD}"/>
-    <hyperlink ref="E27" r:id="rId25" xr:uid="{067D105D-8A09-477A-9677-B9F705D26822}"/>
-    <hyperlink ref="E28" r:id="rId26" xr:uid="{9303FA11-D4E9-4330-9443-839B714D955C}"/>
-    <hyperlink ref="E29" r:id="rId27" xr:uid="{354A71E9-04DF-49CE-A15B-ED13393D44BD}"/>
-    <hyperlink ref="E22" r:id="rId28" xr:uid="{EB40CBF2-F1EC-4970-AD46-77A45CFA5F0E}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{4CCA523A-69EC-480E-8A6B-08F122649A8F}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{F2C1B175-6506-4868-A6AD-8B4810EAF2E0}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{363FBF34-53FD-4093-A383-747877A43D31}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{303A71CE-E844-4304-A1FF-C1E1D6F4BD31}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{5EBF8574-BEB2-48E3-BFE4-87D0F2E8C366}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{879A07A4-2016-4EF2-A409-CDC97AB4DDE1}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{99DEA4A6-58C8-4D1F-8645-03C94EABA977}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{73DACE6E-4662-4800-AC1A-51170BACACCE}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{4C7B5E95-C60C-497D-BFCA-968896310DB8}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{6B10F212-48DA-4EE7-9B93-393285B99B1A}"/>
+    <hyperlink ref="E12" r:id="rId11" xr:uid="{D80CAEF8-3603-4B99-8C3E-F17B4BFD4135}"/>
+    <hyperlink ref="E13" r:id="rId12" xr:uid="{22B71BF5-EE01-4D64-B80B-CE4CE7F586D7}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{5F101619-7F68-4456-8135-816549685EA9}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{CA44A3AE-0ECA-41CE-A2E0-F1A005F24E4C}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{DB0A7188-6075-4E91-A9A6-AE9712A325B9}"/>
+    <hyperlink ref="E17" r:id="rId16" xr:uid="{67D0F36A-F38D-4E8E-8FBE-50360EC469AF}"/>
+    <hyperlink ref="E18" r:id="rId17" xr:uid="{605EEC42-B496-4B32-8ACF-B5DE5728E6A2}"/>
+    <hyperlink ref="E19" r:id="rId18" xr:uid="{9B1642E4-CCBF-44ED-A9C7-05896E0E6379}"/>
+    <hyperlink ref="E20" r:id="rId19" xr:uid="{816E0D7F-47E0-4D80-9B69-547919EE20FC}"/>
+    <hyperlink ref="E21" r:id="rId20" xr:uid="{3B2C1A4A-7D32-4984-902D-74D4D29A1BCE}"/>
+    <hyperlink ref="E23" r:id="rId21" xr:uid="{EAD09DA3-9FE7-4287-B186-78619909D662}"/>
+    <hyperlink ref="E24" r:id="rId22" xr:uid="{0DAECD36-551B-4B56-B6BA-974DAA3C5696}"/>
+    <hyperlink ref="E25" r:id="rId23" xr:uid="{41D36B9F-BF74-4FC9-B5C2-2BFFCB8CB079}"/>
+    <hyperlink ref="E26" r:id="rId24" xr:uid="{37AE9C94-2475-4EAA-BD86-A22AA7BCACA9}"/>
+    <hyperlink ref="E27" r:id="rId25" xr:uid="{1F86EC26-3A7E-4AC5-81AD-977C675DEFC0}"/>
+    <hyperlink ref="E28" r:id="rId26" xr:uid="{B3CDC6F5-C2C6-4675-9AA3-61366AA2DF14}"/>
+    <hyperlink ref="E29" r:id="rId27" xr:uid="{BABF13C5-35A1-4A7F-9FD4-D79F15F3BC60}"/>
+    <hyperlink ref="E30" r:id="rId28" xr:uid="{7E954180-4882-4E1E-A3E2-5C472F7D5944}"/>
+    <hyperlink ref="E31" r:id="rId29" xr:uid="{DE04DCD0-BBAE-4902-8742-62D41AFB5889}"/>
+    <hyperlink ref="E32" r:id="rId30" xr:uid="{3224878A-6C4D-45F7-882E-8D6D15B9F36B}"/>
+    <hyperlink ref="E34" r:id="rId31" xr:uid="{8E7347C1-D6E3-457F-ADA8-D2CD74B2965B}"/>
+    <hyperlink ref="E35" r:id="rId32" xr:uid="{3F548573-8B38-4A70-AD81-B72D42839C7C}"/>
+    <hyperlink ref="E37" r:id="rId33" xr:uid="{66970ED9-0349-4DF8-8381-C9B4FEE16675}"/>
+    <hyperlink ref="E38" r:id="rId34" xr:uid="{C9C71707-0FBD-442F-885C-03A99A824F1D}"/>
+    <hyperlink ref="E39" r:id="rId35" xr:uid="{43847B69-F9FA-459F-9051-FCD02B5E8DF5}"/>
+    <hyperlink ref="E40" r:id="rId36" location="d61330-p1" display="https://www.marmiton.org/recettes/recette_moules-au-chorizo_47729.aspx - d61330-p1" xr:uid="{DBAEAA3E-803F-47A6-8154-906170D25E2A}"/>
+    <hyperlink ref="E41" r:id="rId37" xr:uid="{A37C62D6-259E-4FF1-9498-13CB1900909C}"/>
+    <hyperlink ref="E42" r:id="rId38" xr:uid="{B2DA14F5-E4A1-4261-9ADF-3455D915D422}"/>
+    <hyperlink ref="E43" r:id="rId39" xr:uid="{129605EA-C85B-4307-B467-223B74830206}"/>
+    <hyperlink ref="E44" r:id="rId40" xr:uid="{5A03FF9C-D529-4015-9D60-E81C861A47F7}"/>
+    <hyperlink ref="E45" r:id="rId41" xr:uid="{E0642CBF-3DF4-4D9C-9C57-59947C0C30B5}"/>
+    <hyperlink ref="E46" r:id="rId42" xr:uid="{FA228E07-19B1-46A5-8672-8B2FDFE7049A}"/>
+    <hyperlink ref="E47" r:id="rId43" xr:uid="{25D82D7A-CDE4-45C1-B554-E007F20E57D3}"/>
+    <hyperlink ref="E48" r:id="rId44" xr:uid="{EBBCAB10-A468-4792-B50E-92F590419ADD}"/>
+    <hyperlink ref="E49" r:id="rId45" xr:uid="{4217F5B6-8D90-485C-B130-79433BD26A1F}"/>
+    <hyperlink ref="E50" r:id="rId46" xr:uid="{969EAFA6-286C-482F-80E1-8E5445DBE01E}"/>
+    <hyperlink ref="E51" r:id="rId47" xr:uid="{55C46AE0-4C64-4025-8431-C778F9F7EA5A}"/>
+    <hyperlink ref="E52" r:id="rId48" xr:uid="{A2F9030C-A677-4497-9B31-1BAF31B89C72}"/>
+    <hyperlink ref="E53" r:id="rId49" xr:uid="{0DC3F371-9441-4629-B75C-1288E38FAC69}"/>
+    <hyperlink ref="E54" r:id="rId50" xr:uid="{2514F619-AB84-4447-857C-3A5FEE861806}"/>
+    <hyperlink ref="E55" r:id="rId51" xr:uid="{99314D00-BEFB-4AAB-BD6E-43D3A18E7558}"/>
+    <hyperlink ref="E56" r:id="rId52" xr:uid="{E2F97E8B-B8AC-4E7C-845C-79B25F6EB2D6}"/>
+    <hyperlink ref="E57" r:id="rId53" xr:uid="{E15C5C16-264E-45DB-AA41-A14E8789A860}"/>
+    <hyperlink ref="E58" r:id="rId54" location="utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200428" display="https://www.femmeactuelle.fr/cuisine/cuisine-des-chefs/tous-en-cuisine-la-recette-du-saumon-bouillon-thai-et-riz-aux-petits-pois-de-cyril-lignac-2093981?fbclid=IwAR1uQpqeHZrunEVAuFEKqmhxqKRyuwsasWwBZFimhboJryw9CMyjR1coePg - utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200428" xr:uid="{E94D3C6E-1CF3-42A6-8836-3228550DCA38}"/>
+    <hyperlink ref="E59" r:id="rId55" xr:uid="{7FEAC0B4-A15E-429F-95E5-86CDE85F9C70}"/>
+    <hyperlink ref="E60" r:id="rId56" xr:uid="{BE676F13-88DC-45F6-B97B-A467502104A9}"/>
+    <hyperlink ref="E61" r:id="rId57" xr:uid="{0A8A47C8-F082-4F5D-87A6-180830BECA7E}"/>
+    <hyperlink ref="E62" r:id="rId58" xr:uid="{D6553FDA-07A5-4B27-A698-D128A8CAAC0D}"/>
+    <hyperlink ref="E63" r:id="rId59" xr:uid="{8B6560A7-3F23-44AF-8591-B14C0AF57009}"/>
+    <hyperlink ref="E64" r:id="rId60" xr:uid="{2C8EB56E-C727-4BAB-8BAC-A95E0EE68572}"/>
+    <hyperlink ref="E65" r:id="rId61" xr:uid="{CBFB933F-81C6-4B8B-A464-2F2B8A056362}"/>
+    <hyperlink ref="E66" r:id="rId62" xr:uid="{95F80C7F-D163-4718-9315-DEA80E00BB81}"/>
+    <hyperlink ref="E67" r:id="rId63" xr:uid="{27FE9C3A-3DFC-409D-8F19-CF2D7FDA11F2}"/>
+    <hyperlink ref="E68" r:id="rId64" xr:uid="{8CE5BF85-2BB1-4298-ABC5-0FC2D8421BFF}"/>
+    <hyperlink ref="E69" r:id="rId65" xr:uid="{072CF68D-7ED8-4B6D-8B87-3ED8E20DDEBA}"/>
+    <hyperlink ref="E70" r:id="rId66" xr:uid="{E5E8B2F5-1E23-45A0-B1BE-9C06E1D4C8ED}"/>
+    <hyperlink ref="E71" r:id="rId67" xr:uid="{228048DB-F439-4E53-97BE-62111DDB331F}"/>
+    <hyperlink ref="E72" r:id="rId68" xr:uid="{D1D18792-5FFB-4747-9FB5-071A2D9FC13A}"/>
+    <hyperlink ref="E73" r:id="rId69" xr:uid="{D9B6AD06-BC90-4268-9332-4B96EDA1BBCA}"/>
+    <hyperlink ref="E74" r:id="rId70" xr:uid="{D059DB48-2DE0-462F-BE65-03DCD0CB9DCE}"/>
+    <hyperlink ref="E75" r:id="rId71" xr:uid="{C6687483-0D81-48E5-B16D-220AD9782DFB}"/>
+    <hyperlink ref="E76" r:id="rId72" xr:uid="{D2144BE8-0475-4B94-A4B3-58A5FD1B3757}"/>
+    <hyperlink ref="E77" r:id="rId73" xr:uid="{B56A7FF8-A000-4F9F-8F85-1DCEF74974E5}"/>
+    <hyperlink ref="E78" r:id="rId74" xr:uid="{3EE74E01-4A6F-4592-8322-93D5AABE9164}"/>
+    <hyperlink ref="E79" r:id="rId75" xr:uid="{83B06DE1-6BDB-469E-BEDC-26BAA6AC2B5B}"/>
+    <hyperlink ref="E80" r:id="rId76" xr:uid="{EE268E3D-56C4-4906-B232-989989AF3CAC}"/>
+    <hyperlink ref="E81" r:id="rId77" xr:uid="{FA12B1D6-7F68-4039-A94E-EDBC770D7254}"/>
+    <hyperlink ref="E82" r:id="rId78" xr:uid="{1E6DF1F7-BB5C-4E39-A2BB-851FDF817627}"/>
+    <hyperlink ref="E83" r:id="rId79" display="https://www.cuisineactuelle.fr/recettes/veloute-de-chou-fleur-et-moules-a-la-dieppoise-212783?utm_source=welcomingentreeplatdessert" xr:uid="{07F4287E-1922-446E-B7A7-E2B6C585DB11}"/>
+    <hyperlink ref="E84" r:id="rId80" xr:uid="{5C0F5D92-BC58-47AE-9B06-093E15804D1B}"/>
+    <hyperlink ref="E85" r:id="rId81" xr:uid="{79BCD98D-BD95-453E-A6CB-68289C8A80AC}"/>
+    <hyperlink ref="E86" r:id="rId82" xr:uid="{29ED75DB-8E0B-4989-908D-F20D33172C6F}"/>
+    <hyperlink ref="E87" r:id="rId83" xr:uid="{886A11EA-598F-4C27-BE0A-07659F850A0E}"/>
+    <hyperlink ref="E88" r:id="rId84" location="utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200512" display="https://www.cuisineactuelle.fr/recettes/risotto-au-saumon-et-a-loseille-193308 - utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200512" xr:uid="{36288E5D-B4B3-4DF4-8AA4-4CA0AC506CCA}"/>
+    <hyperlink ref="E89" r:id="rId85" xr:uid="{AA9180A5-48F4-4079-A992-1D2C96093CA5}"/>
+    <hyperlink ref="E90" r:id="rId86" xr:uid="{E3E781F7-0686-4D23-85D2-3DC0F80531FF}"/>
+    <hyperlink ref="E91" r:id="rId87" xr:uid="{9F1CD3EA-53C2-46F9-B15D-44FF9CF4BADE}"/>
+    <hyperlink ref="E92" r:id="rId88" xr:uid="{C79DEA93-452E-4278-952A-8E74BCFAB65D}"/>
+    <hyperlink ref="E93" r:id="rId89" xr:uid="{5941E5DC-2ECA-4F9D-B76F-2FFA66AB7191}"/>
+    <hyperlink ref="E94" r:id="rId90" xr:uid="{7CDC0D26-1EC7-4AE6-8BEC-76060B74A45F}"/>
+    <hyperlink ref="E95" r:id="rId91" xr:uid="{4406AE4F-CFBA-4CB8-A32C-2A9ABE88DAE3}"/>
+    <hyperlink ref="E96" r:id="rId92" xr:uid="{DFA8EAEC-49BE-4E88-ABCA-719D12159A6E}"/>
+    <hyperlink ref="E97" r:id="rId93" display="https://www.cuisineactuelle.fr/recettes/blanquette-de-saumon-286121?utm_source=welcomingentreeplatdessert&amp;utm_medium=cpc&amp;utm_campaign=pmo_cac_article" xr:uid="{CC0214C7-A83C-4AE9-AD43-031D18818B5C}"/>
+    <hyperlink ref="E98" r:id="rId94" xr:uid="{8A04214C-A437-43CE-B1BE-28DA7E3B650D}"/>
+    <hyperlink ref="E99" r:id="rId95" xr:uid="{76818778-AC42-4D1D-B570-CFDCA661F1CF}"/>
+    <hyperlink ref="E100" r:id="rId96" xr:uid="{10ABB693-033E-44F2-88E8-55C27E220DBE}"/>
+    <hyperlink ref="E101" r:id="rId97" xr:uid="{7B4F4CAE-55C4-4351-B067-0F2BB0527473}"/>
+    <hyperlink ref="E102" r:id="rId98" xr:uid="{87C98986-2D60-4805-A0BA-082C8E64B253}"/>
+    <hyperlink ref="E103" r:id="rId99" xr:uid="{7326D242-7E41-434D-87C3-6BD15CA91783}"/>
+    <hyperlink ref="E104" r:id="rId100" xr:uid="{9254D943-0A34-4468-BC9A-F98E2A7DCFD2}"/>
+    <hyperlink ref="E105" r:id="rId101" xr:uid="{671DE20D-0F5C-4F76-AFDC-6805FC2C05A7}"/>
+    <hyperlink ref="E106" r:id="rId102" xr:uid="{553B7DD1-90FE-431C-B908-0B0D32032296}"/>
+    <hyperlink ref="E107" r:id="rId103" xr:uid="{BB8C8A3C-14CE-4301-BB3C-0072AC284C7B}"/>
+    <hyperlink ref="E108" r:id="rId104" xr:uid="{88E559F7-0BD7-4842-90D6-BF960FA1EDCC}"/>
+    <hyperlink ref="E109" r:id="rId105" xr:uid="{832BA905-97CB-4EC5-A650-BDD10DBFD592}"/>
+    <hyperlink ref="E110" r:id="rId106" xr:uid="{D2EAF065-752B-4DDB-8D3B-2A9C32C5554F}"/>
+    <hyperlink ref="E111" r:id="rId107" xr:uid="{7D607108-0FA9-4F0C-804A-D70F87FE2378}"/>
+    <hyperlink ref="E112" r:id="rId108" xr:uid="{8736D83B-4001-4E42-86CC-00FB619E2D2B}"/>
+    <hyperlink ref="E113" r:id="rId109" xr:uid="{5B97E86B-A496-467C-83A3-BA3C413176F1}"/>
+    <hyperlink ref="E114" r:id="rId110" xr:uid="{7AAD8093-0F78-473E-B85E-1031BE8FDD7E}"/>
+    <hyperlink ref="E115" r:id="rId111" xr:uid="{C326C386-E1DD-4CFC-89DA-152255D71034}"/>
+    <hyperlink ref="E116" r:id="rId112" xr:uid="{BF1782E3-9AD8-40EA-8A05-9323C61AA22E}"/>
+    <hyperlink ref="E117" r:id="rId113" xr:uid="{8EAE3E2A-85D8-432A-94D5-085EC2E4A347}"/>
+    <hyperlink ref="E118" r:id="rId114" xr:uid="{A0488276-782F-4417-B435-38FA1AFFAF5C}"/>
+    <hyperlink ref="E119" r:id="rId115" xr:uid="{0313814B-59ED-482F-9B8F-5C09D8574E84}"/>
+    <hyperlink ref="E120" r:id="rId116" xr:uid="{323E5705-BC35-419F-BA7D-1E358895F963}"/>
+    <hyperlink ref="E121" r:id="rId117" xr:uid="{FB71CE64-A822-4BA2-B327-5D6C9503E0AF}"/>
+    <hyperlink ref="E122" r:id="rId118" xr:uid="{898B2884-C587-4B9A-B479-8276B86E3345}"/>
+    <hyperlink ref="E123" r:id="rId119" xr:uid="{C76A0C99-CFF3-4801-AB4C-6650BF7EDA63}"/>
+    <hyperlink ref="E124" r:id="rId120" xr:uid="{B74C9A01-60E4-4140-865E-DFA9EA9AA48E}"/>
+    <hyperlink ref="E125" r:id="rId121" xr:uid="{64606858-7D04-428C-87D7-31AB0F594492}"/>
+    <hyperlink ref="E126" r:id="rId122" xr:uid="{0A5DBDC0-1D0B-4338-9F1B-0D3C554E87F1}"/>
+    <hyperlink ref="E127" r:id="rId123" xr:uid="{CA3B42CF-32C9-4CE8-9E15-67C49A132677}"/>
+    <hyperlink ref="E128" r:id="rId124" xr:uid="{E8070508-0232-4A7F-B0D5-FCBD28D0EA4F}"/>
+    <hyperlink ref="E129" r:id="rId125" xr:uid="{A389B2CF-C313-4762-917F-8C7355D1D1DD}"/>
+    <hyperlink ref="E130" r:id="rId126" xr:uid="{929301A7-E1AE-4794-A3CD-EC721DB7E06C}"/>
+    <hyperlink ref="E131" r:id="rId127" xr:uid="{488F53BA-4A4F-4812-8F20-48CDBD9A61F7}"/>
+    <hyperlink ref="E132" r:id="rId128" xr:uid="{FF82A693-8EB0-48A4-B76E-5CD3EE26E627}"/>
+    <hyperlink ref="E133" r:id="rId129" location="utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200326" display="https://www.cuisineactuelle.fr/recettes/ravioles-de-royans-a-la-coriandre-et-au-piment-192747?fbclid=IwAR2Y0EPQx-oUAScCrcQDz4dXwHvIJopf0u0_nYjGCt9yN1KGGOkLMzfraT4 - utm_source=welcomingCuisine&amp;utm_medium=cpc&amp;utm_campaign=20200326" xr:uid="{66E1DAA8-9932-49C6-9F1B-2FBAAC726486}"/>
+    <hyperlink ref="E134" r:id="rId130" xr:uid="{6EB72151-1464-4771-832B-193682E25C6D}"/>
+    <hyperlink ref="E135" r:id="rId131" xr:uid="{B42E1162-E064-463E-897E-577FBF62DFA7}"/>
+    <hyperlink ref="E22" r:id="rId132" xr:uid="{151AB233-B4C7-4ABE-A438-AA1C1057CC61}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
